--- a/airtable_json_uploader/json_files/Airtable - ShineSky.xlsx
+++ b/airtable_json_uploader/json_files/Airtable - ShineSky.xlsx
@@ -112,7 +112,7 @@
     <t>simple</t>
   </si>
   <si>
-    <t>Top View</t>
+    <t>Black Neon</t>
   </si>
   <si>
     <t>draft</t>
@@ -130,50 +130,25 @@
     <t>10W/m | 2700K | 24V | IP65 | 10mm (W) x 10mm (H) | 5,000mm (L) | Black</t>
   </si>
   <si>
-    <t>Power Consumption Rate | CCT | Voltage | IP Rating | Dimension | Length | Finish</t>
-  </si>
-  <si>
-    <t>{ "SKU": "TV1010-10W-2.7K-IP65-Black", "Power Consumption Rate": "10W/m", "CCT": "2700K", "Voltage": "24V", "IP Rating": "IP65", "Dimension": "10mm (W) x 10mm (H)", "Length": "5,000mm (L)", "Finish": "Black" }</t>
-  </si>
-  <si>
-    <t>{ "Power Consumption Rate": "10W/m", "CCT": [ "2700K", "3000K", "4000K", "6000K" ], "Voltage": "24V", "IP Rating": "IP65", "Dimension": "10mm (W) x 10mm (H)", "Length": "5,000mm (L)", "Finish": "Black" }</t>
+    <t>Power Consumption Rate | Color Temperature | Voltage | IP Rating | Dimension | Length | Finish</t>
   </si>
   <si>
     <t>{
-"Options": {
-"Power Consumption Rate": [
-{"name": "10W/m", "id": "101"}
-],
-"CCT": [
-{"name": "2700K", "id": "102"},
-{"name": "3000K", "id": "103"},
-{"name": "4000K", "id": "104"},
-{"name": "6000K", "id": "105"}
-],
-"Voltage": [
-{"name": "24V", "id": "106"}
-],
-"IP Rating": [
-{"name": "IP65", "id": "107"}
-],
-"Dimension": [
-{"name": "10mm (W) x 10mm (H)", "id": "108"}
-],
-"Length": [
-{"name": "5,000mm (L)", "id": "109"}
-],
-"Finish": [
-{"name": "Black", "id": "110"}
-]
-},
-"Constraints": {},
-"sku_mappings": [
-{ "sku": "TV1010-10W-2.7K-IP65-Black", "combination": ["101", "102", "106", "107", "108", "109", "110"] },
-{ "sku": "TV1010-10W-3K-IP65-Black", "combination": ["101", "103", "106", "107", "108", "109", "110"] },
-{ "sku": "TV1010-10W-4K-IP65-Black", "combination": ["101", "104", "106", "107", "108", "109", "110"] },
-{ "sku": "TV1010-10W-6K-IP65-Black", "combination": ["101", "105", "106", "107", "108", "109", "110"] }
-]
+"Power Consumption Rate": "10W/m",
+"Color Temperature": "2700K",
+"Voltage": "24V",
+"IP Rating": "IP65",
+"Dimension": "10mm (W) x 10mm (H)",
+"Length": "5,000mm (L)",
+"Finish": "Black",
+"SKU": "TV1010-10W-2.7K-IP65-Black"
 }</t>
+  </si>
+  <si>
+    <t>{ "Power Consumption Rate": "10W/m", "Color Temperature": [ "2700K", "3000K", "4000K", "6000K" ], "Voltage": "24V", "IP Rating": "IP65", "Dimension": "10mm (W) x 10mm (H)", "Length": "5,000mm (L)", "Finish": "Black", "SKU": [ "TV1010-10W-2.7K-IP65-Black", "TV1010-10W-3K-IP65-Black", "TV1010-10W-4K-IP65-Black", "TV1010-10W-6K-IP65-Black" ] }</t>
+  </si>
+  <si>
+    <t>{ "Options": { "Power Consumption Rate": [ {"name": "10W/m", "id": "101"} ], "Color Temperature": [ {"name": "2700K", "id": "102"}, {"name": "3000K", "id": "103"}, {"name": "4000K", "id": "104"}, {"name": "6000K", "id": "105"} ], "Voltage": [ {"name": "24V", "id": "106"} ], "IP Rating": [ {"name": "IP65", "id": "107"} ], "Dimension": [ {"name": "10mm (W) x 10mm (H)", "id": "108"} ], "Length": [ {"name": "5,000mm (L)", "id": "109"} ], "Finish": [ {"name": "Black", "id": "110"} ] }, "Constraints": {}, "sku_mappings": [ { "sku": "TV1010-10W-2.7K-IP65-Black", "combination": ["101", "102", "106", "107", "108", "109", "110"] }, { "sku": "TV1010-10W-3K-IP65-Black", "combination": ["101", "103", "106", "107", "108", "109", "110"] }, { "sku": "TV1010-10W-4K-IP65-Black", "combination": ["101", "104", "106", "107", "108", "109", "110"] }, { "sku": "TV1010-10W-6K-IP65-Black", "combination": ["101", "105", "106", "107", "108", "109", "110"] } ] }</t>
   </si>
   <si>
     <t>CHINA - Shine Sky</t>
@@ -194,7 +169,16 @@
     <t>10W/m | 3000K | 24V | IP65 | 10mm (W) x 10mm (H) | 5,000mm (L) | Black</t>
   </si>
   <si>
-    <t>{ "SKU": "TV1010-10W-3K-IP65-Black", "Power Consumption Rate": "10W/m", "CCT": "3000K", "Voltage": "24V", "IP Rating": "IP65", "Dimension": "10mm (W) x 10mm (H)", "Length": "5,000mm (L)", "Finish": "Black" }</t>
+    <t>{
+"Power Consumption Rate": "10W/m",
+"Color Temperature": "3000K",
+"Voltage": "24V",
+"IP Rating": "IP65",
+"Dimension": "10mm (W) x 10mm (H)",
+"Length": "5,000mm (L)",
+"Finish": "Black",
+"SKU": "TV1010-10W-3K-IP65-Black"
+}</t>
   </si>
   <si>
     <t>SK-NTB1010V24-C30</t>
@@ -206,7 +190,16 @@
     <t>10W/m | 4000K | 24V | IP65 | 10mm (W) x 10mm (H) | 5,000mm (L) | Black</t>
   </si>
   <si>
-    <t>{ "SKU": "TV1010-10W-4K-IP65-Black", "Power Consumption Rate": "10W/m", "CCT": "4000K", "Voltage": "24V", "IP Rating": "IP65", "Dimension": "10mm (W) x 10mm (H)", "Length": "5,000mm (L)", "Finish": "Black" }</t>
+    <t>{
+"Power Consumption Rate": "10W/m",
+"Color Temperature": "4000K",
+"Voltage": "24V",
+"IP Rating": "IP65",
+"Dimension": "10mm (W) x 10mm (H)",
+"Length": "5,000mm (L)",
+"Finish": "Black",
+"SKU": "TV1010-10W-4K-IP65-Black"
+}</t>
   </si>
   <si>
     <t>SK-NTB1010V24-C40</t>
@@ -218,7 +211,16 @@
     <t>10W/m | 6000K | 24V | IP65 | 10mm (W) x 10mm (H) | 5,000mm (L) | Black</t>
   </si>
   <si>
-    <t>{ "SKU": "TV1010-10W-6K-IP65-Black", "Power Consumption Rate": "10W/m", "CCT": "6000K", "Voltage": "24V", "IP Rating": "IP65", "Dimension": "10mm (W) x 10mm (H)", "Length": "5,000mm (L)", "Finish": "Black" }</t>
+    <t>{
+"Power Consumption Rate": "10W/m",
+"Color Temperature": "6000K",
+"Voltage": "24V",
+"IP Rating": "IP65",
+"Dimension": "10mm (W) x 10mm (H)",
+"Length": "5,000mm (L)",
+"Finish": "Black",
+"SKU": "TV1010-10W-6K-IP65-Black"
+}</t>
   </si>
   <si>
     <t>SK-NTB1010V24-C65</t>
@@ -833,54 +835,91 @@
 ### SCHEMA DEFINITIONS
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
-- Light Color (Example Warm White, RGBW, TW, RGB, RED)
-- CCT (Example 3000K, 4000K)
-- Voltage (Example 20V, 12V/24V)
+- Color Temperature (Example 2200K, 2700K, 3000K, 4000K, 5300K, RGBW (3000K), TW (2700K-5300K), TW (2700K-6500K), 2700K &amp; 3000K, RGB, RED, RGB+TW (2700K-6500K), 2700K-4000K, 2300K-4000K)
+- Voltage (Example "&amp;"20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68, IP20)
-- Impact Strength ("&amp;"Example IK10, IK10 with Neon-AluProfile-1617)
+- Impact Strength (Example IK10, IK10 with Neon-AluProfile-1617)
 - Optics (Example SYS30°)
-- Finish (Example Black finish, Silver)
-- Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
-- Dimension (Example 53mm (W) x 14mm"&amp;" (H), 480mm (L) x 240mm (W))
+- Finish (Example Black, Silver)
+- Channel Configuration (Example Singel-Sided, "&amp;"Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
+- Dimension (Example 53mm (W) x 14mm (H), 480mm (L) x 240mm (W))
 - Length (Example Max 11,000mm (L), 5,000mm (L))
-- Strip Width (Example 8mm, 12mm, 8mm (W))
-- Depth (Example 13mm (D))
+- Strip Width (Example 8mm, 12mm)
 - Power Consumption Rate (Example 8W/m, 5W/m)
-- Profile Length (Example 1,000mm)
-- AC Phase-Cut (Example Tr"&amp;"iac)
+-"&amp;" Profile Length (Example 1,000mm)
+- AC Phase-Cut (Example Triac)
 - Current Sinking (Example 0-10V)
 - Current Sourcing (Example 1-10V)
 - Duty Cycle (Example PWM)
 - Variable Resistance (Example Potentiometer)
-- Resolution (Example 12 Pixels/m)
-- Control Protocol (Example DMX, SPI)
+- Pixel (Example 12 Pixels/m)
+- Control Protocol"&amp;" (Example DMX, SPI)
 - Cut Interval (Example Free Cut)
--"&amp;" Glare Control (Example Honeycomb Anti Glare Louvre)
+- Glare Control (Example Honeycomb Anti Glare Louvre)
 - Beam Angle (Example 30°, 36°, 360°)
+- View (Example Top View, Side View)
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding labels mentioned above separated by pipes ('|'). 
+1. Output ONLY the corresponding labels mentio"&amp;"ned above separated by pipes ('|'). 
 2. Do not include the values in your output.
-3. Do not i"&amp;"nclude any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the number of values provided in the input.
+3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
+4. The number of labels in your output must exactly match the number of value"&amp;"s provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-In"&amp;"put: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black finish
+Input: 1.2W | SYM30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black"&amp;"
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
-Generate outpu"&amp;"t for the values text ""&amp;M2)"),"Power Consumption Rate | CCT | Voltage | IP Rating | Dimension | Length | Finish")</f>
-        <v>Power Consumption Rate | CCT | Voltage | IP Rating | Dimension | Length | Finish</v>
+Generate output for the values text ""&amp;M2)"),"Power Consumption Rate | Color Temperature | Voltage | IP Rating | Dimension | Length | Finish")</f>
+        <v>Power Consumption Rate | Color Temperature | Voltage | IP Rating | Dimension | Length | Finish</v>
       </c>
       <c r="O2" s="13" t="s">
         <v>39</v>
       </c>
       <c r="P2" s="12" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N2&amp;"" and values ""&amp;M2&amp;"" separated by character '|' and Using ""&amp;L2&amp;"" and key as 'SKU', Create a JSON object"")"),"{ ""SKU"": ""TV1010-10W-2.7K-IP65-Black"", ""Power Consumption Rate"": ""10W/m"", ""CCT"": ""2700K"", ""Voltage"": ""24V"", ""IP Rating"": ""IP65"", ""Dimension"": ""10mm (W) x 10mm (H)"", ""Length"": ""5,000mm (L)"", ""Finish"": ""Black"" }")</f>
-        <v>{ "SKU": "TV1010-10W-2.7K-IP65-Black", "Power Consumption Rate": "10W/m", "CCT": "2700K", "Voltage": "24V", "IP Rating": "IP65", "Dimension": "10mm (W) x 10mm (H)", "Length": "5,000mm (L)", "Finish": "Black" }</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O2&amp;"", Values: ""&amp;M2&amp; "" and SKU Code: ""&amp;L2"&amp;")"),"{
+""Power Consumption Rate"": ""10W/m"",
+""Color Temperature"": ""2700K"",
+""Voltage"": ""24V"",
+""IP Rating"": ""IP65"",
+""Dimension"": ""10mm (W) x 10mm (H)"",
+""Length"": ""5,000mm (L)"",
+""Finish"": ""Black"",
+""SKU"": ""TV1010-10W-2.7K-IP65-Black""
+}")</f>
+        <v>{
+"Power Consumption Rate": "10W/m",
+"Color Temperature": "2700K",
+"Voltage": "24V",
+"IP Rating": "IP65",
+"Dimension": "10mm (W) x 10mm (H)",
+"Length": "5,000mm (L)",
+"Finish": "Black",
+"SKU": "TV1010-10W-2.7K-IP65-Black"
+}</v>
       </c>
       <c r="Q2" s="13" t="s">
         <v>40</v>
@@ -892,8 +931,8 @@
 2. If a key has the same value across all objects, render it as a single primitive value (string/number).  
 3. If a key has multiple distinct values across the objects, combine them into an array containing only the unique values (deduplicated).  
 4. Ma"&amp;"intain a clean, properly formatted, and valid JSON structure.  
-Here is the input data:"", Q2:Q5)"),"{ ""Power Consumption Rate"": ""10W/m"", ""CCT"": [ ""2700K"", ""3000K"", ""4000K"", ""6000K"" ], ""Voltage"": ""24V"", ""IP Rating"": ""IP65"", ""Dimension"": ""10mm (W) x 10mm (H)"", ""Length"": ""5,000mm (L)"", ""Finish"": ""Black"" }")</f>
-        <v>{ "Power Consumption Rate": "10W/m", "CCT": [ "2700K", "3000K", "4000K", "6000K" ], "Voltage": "24V", "IP Rating": "IP65", "Dimension": "10mm (W) x 10mm (H)", "Length": "5,000mm (L)", "Finish": "Black" }</v>
+Here is the input data:"", Q2:Q5)"),"{ ""Power Consumption Rate"": ""10W/m"", ""Color Temperature"": [ ""2700K"", ""3000K"", ""4000K"", ""6000K"" ], ""Voltage"": ""24V"", ""IP Rating"": ""IP65"", ""Dimension"": ""10mm (W) x 10mm (H)"", ""Length"": ""5,000mm (L)"", ""Finish"": ""Black"", ""SK"&amp;"U"": [ ""TV1010-10W-2.7K-IP65-Black"", ""TV1010-10W-3K-IP65-Black"", ""TV1010-10W-4K-IP65-Black"", ""TV1010-10W-6K-IP65-Black"" ] }")</f>
+        <v>{ "Power Consumption Rate": "10W/m", "Color Temperature": [ "2700K", "3000K", "4000K", "6000K" ], "Voltage": "24V", "IP Rating": "IP65", "Dimension": "10mm (W) x 10mm (H)", "Length": "5,000mm (L)", "Finish": "Black", "SKU": [ "TV1010-10W-2.7K-IP65-Black", "TV1010-10W-3K-IP65-Black", "TV1010-10W-4K-IP65-Black", "TV1010-10W-6K-IP65-Black" ] }</v>
       </c>
       <c r="S2" s="14" t="s">
         <v>41</v>
@@ -902,45 +941,45 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a product catalog configuration expert. Your task is to analyze a list of valid product variant combinations (provided as JSON lines/objects) and generate two JSON structures: """"Options"""" and """"Constraints"""".
 ### Instructions:
 1. **"&amp;"Extract Options:**
-   - Group all unique values by their attribute keys (e.g., Power, Optics, CCT, IP Rating, Impact Strength).
-   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and incrementing by 1 in "&amp;"the order they appear.
+   - Group all unique values by their attribute keys (e.g., Power, Optics, Color Temperature, IP Rating, Impact Strength).
+   - Assign a unique sequential integer string ID to every attribute value, starting from """"101"""" and increme"&amp;"nting by 1 in the order they appear.
    - Format each attribute as an array of objects: `[{""""name"""": """"VALUE"""", """"id"""": """"ID""""}]`.
 2. **Determine Constraints (Incompatibilities):**
-   - Identify attribute pairs that are impossible or missing from the v"&amp;"alid combinations.
+   - Identify attribute pairs that are impossible or miss"&amp;"ing from the valid combinations.
    - Specifically, map an ID of an Option Value to an array of Option Value IDs that **cannot** be selected with it.
    - Output constraints in the format: `""""OPTION_ID"""": [INCOMPATIBLE_OPTION_ID]`.
-   - Only list meaningful non-emp"&amp;"ty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
+   - Only list mean"&amp;"ingful non-empty constraints. Express constraints using the primary driving factor (e.g., optic limitation over CCT).
 3. **Determine sku_mappings:**
-   - Identify the valid combination and create a array with sku and combination containing array of options ID
-4. **O"&amp;"utput Format:**
+   - Identify the valid combination and create a array with sku and combination containing array of optio"&amp;"ns ID
+4. **Output Format:**
    - Return strictly valid JSON containing two root keys: """"Options"""", """"Constraints"""" and """"sku_mappings"""".
    - Do not wrap the JSON in conversational filler text.
 ---
 ### Example Input:
-{""""SKU"""":""""HRS001"""", """"Pow"&amp;"er"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"CCT"""""&amp;": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Stre"&amp;"ngth"""": """"IK10""""}
-{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"CCT"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
-{""""SKU"""":""""HRS005"""", """"Power"""&amp;""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"CCT"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS00"&amp;"1"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM30°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS002"""", """"Power"""": """"1.2W"""", """"Optics"""":"&amp;" """"SYM30°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS003"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"300"&amp;"0K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS004"""", """"Power"""": """"1.2W"""", """"Optics"""": """"SYM60°"""", """"Color Temperature"""": """"4000K"""", """"IP Rating"""": """"IP67"""", """"Impact"&amp;" Strength"""": """"IK10""""}
+{""""SKU"""":""""HRS005"""", """"Power"""": """"1.2W"""", """"Optics"""": """"ASYM50°"""", """"Color Temperature"""": """"3000K"""", """"IP Rating"""": """"IP67"""", """"Impact Strength"""": """"IK10""""}
 ### Example Output:
-{
+"&amp;"{
   """"Options"""": {
     """"Power"""": [
-      {""""name"""": """"1.2W"""", """""&amp;"id"""": """"101""""}
+      {""""name"""": """"1.2W"""", """"id"""": """"101""""}
     ],
     """"Optics"""": [
       {""""name"""": """"SYM30°"""", """"id"""": """"102""""},
-      {""""name"""": """"SYM60°"""", """"id"""": """"103""""},
+      {""""name"""": """"SYM60°"""", """"id"""": """"103"""&amp;"""},
       {""""name"""": """"ASYM50°"""", """"id"""": """"104""""}
     ],
-    """"C"&amp;"CT"""": [
+    """"Color Temperature"""": [
       {""""name"""": """"3000K"""", """"id"""": """"105""""},
       {""""name"""": """"4000K"""", """"id"""": """"106""""}
     ],
-    """"IP Rating"""": [
+    """"IP Rating"&amp;""""": [
       {""""name"""": """"IP67"""", """"id"""": """"107""""}
     ],
-    """"Impact Strength"&amp;""""": [
+    """"Impact Strength"""": [
       {""""name"""": """"IK10"""", """"id"""": """"108""""}
     ]
   },
@@ -948,91 +987,23 @@
     """"104"""": [106]
   },
 """"sku_mappings"""": [
-      { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+ "&amp;"     { """"sku"""": """"HRS001"""", """"combination"""": [""""101"""", """"102"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS002"""", """"combination"""": [""""101"""", """"102"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+  "&amp;"    { """"sku"""": """"HRS003"""", """"combination"""": [""""101"""", """"103"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS004"""", """"combination"""": [""""101"""", """"103"""", """"106"""", """"107"""", """"108""""] },
-      { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", "&amp;"""""107"""", """"108""""] },
+   "&amp;"   { """"sku"""": """"HRS005"""", """"combination"""": [""""101"""", """"104"""", """"105"""", """"107"""", """"108""""] },
       { """"sku"""": """"HRS006"""", """"combination"""": [""""101"""", """"104"""", """"106"""", """"107"""", """"108""""] }
-    ]
+    ]"&amp;"
 }
-Process the following product variant combinations and output the """"Options"""" and """"C"&amp;"onstraints"""" JSON:"", Q2:Q5)"),"{
-""Options"": {
-""Power Consumption Rate"": [
-{""name"": ""10W/m"", ""id"": ""101""}
-],
-""CCT"": [
-{""name"": ""2700K"", ""id"": ""102""},
-{""name"": ""3000K"", ""id"": ""103""},
-{""name"": ""4000K"", ""id"": ""104""},
-{""name"": ""6000K"", ""id"": ""105"&amp;"""}
-],
-""Voltage"": [
-{""name"": ""24V"", ""id"": ""106""}
-],
-""IP Rating"": [
-{""name"": ""IP65"", ""id"": ""107""}
-],
-""Dimension"": [
-{""name"": ""10mm (W) x 10mm (H)"", ""id"": ""108""}
-],
-""Length"": [
-{""name"": ""5,000mm (L)"", ""id"": ""109""}
-],
-"&amp;"""Finish"": [
-{""name"": ""Black"", ""id"": ""110""}
-]
-},
-""Constraints"": {},
-""sku_mappings"": [
-{ ""sku"": ""TV1010-10W-2.7K-IP65-Black"", ""combination"": [""101"", ""102"", ""106"", ""107"", ""108"", ""109"", ""110""] },
-{ ""sku"": ""TV1010-10W-3K-IP"&amp;"65-Black"", ""combination"": [""101"", ""103"", ""106"", ""107"", ""108"", ""109"", ""110""] },
-{ ""sku"": ""TV1010-10W-4K-IP65-Black"", ""combination"": [""101"", ""104"", ""106"", ""107"", ""108"", ""109"", ""110""] },
-{ ""sku"": ""TV1010-10W-6K-IP65-Bl"&amp;"ack"", ""combination"": [""101"", ""105"", ""106"", ""107"", ""108"", ""109"", ""110""] }
-]
-}")</f>
-        <v>{
-"Options": {
-"Power Consumption Rate": [
-{"name": "10W/m", "id": "101"}
-],
-"CCT": [
-{"name": "2700K", "id": "102"},
-{"name": "3000K", "id": "103"},
-{"name": "4000K", "id": "104"},
-{"name": "6000K", "id": "105"}
-],
-"Voltage": [
-{"name": "24V", "id": "106"}
-],
-"IP Rating": [
-{"name": "IP65", "id": "107"}
-],
-"Dimension": [
-{"name": "10mm (W) x 10mm (H)", "id": "108"}
-],
-"Length": [
-{"name": "5,000mm (L)", "id": "109"}
-],
-"Finish": [
-{"name": "Black", "id": "110"}
-]
-},
-"Constraints": {},
-"sku_mappings": [
-{ "sku": "TV1010-10W-2.7K-IP65-Black", "combination": ["101", "102", "106", "107", "108", "109", "110"] },
-{ "sku": "TV1010-10W-3K-IP65-Black", "combination": ["101", "103", "106", "107", "108", "109", "110"] },
-{ "sku": "TV1010-10W-4K-IP65-Black", "combination": ["101", "104", "106", "107", "108", "109", "110"] },
-{ "sku": "TV1010-10W-6K-IP65-Black", "combination": ["101", "105", "106", "107", "108", "109", "110"] }
-]
-}</v>
+Process the following product variant combinations and output the """"Options"""" and """"Constraints"""" JSON:"", Q2:Q5)"),"{ ""Options"": { ""Power Consumption Rate"": [ {""name"": ""10W/m"", ""id"": ""101""} ], ""Color Temperature"": [ {""name"": ""2700K"", ""id"": ""102""}, {""name"": ""3000K"", ""id"": ""103""}, {""name"": ""4000K"", ""id"": ""104""}, {""name"": ""6000K"","&amp;" ""id"": ""105""} ], ""Voltage"": [ {""name"": ""24V"", ""id"": ""106""} ], ""IP Rating"": [ {""name"": ""IP65"", ""id"": ""107""} ], ""Dimension"": [ {""name"": ""10mm (W) x 10mm (H)"", ""id"": ""108""} ], ""Length"": [ {""name"": ""5,000mm (L)"", ""id"""&amp;": ""109""} ], ""Finish"": [ {""name"": ""Black"", ""id"": ""110""} ] }, ""Constraints"": {}, ""sku_mappings"": [ { ""sku"": ""TV1010-10W-2.7K-IP65-Black"", ""combination"": [""101"", ""102"", ""106"", ""107"", ""108"", ""109"", ""110""] }, { ""sku"": ""TV"&amp;"1010-10W-3K-IP65-Black"", ""combination"": [""101"", ""103"", ""106"", ""107"", ""108"", ""109"", ""110""] }, { ""sku"": ""TV1010-10W-4K-IP65-Black"", ""combination"": [""101"", ""104"", ""106"", ""107"", ""108"", ""109"", ""110""] }, { ""sku"": ""TV1010-"&amp;"10W-6K-IP65-Black"", ""combination"": [""101"", ""105"", ""106"", ""107"", ""108"", ""109"", ""110""] } ] }")</f>
+        <v>{ "Options": { "Power Consumption Rate": [ {"name": "10W/m", "id": "101"} ], "Color Temperature": [ {"name": "2700K", "id": "102"}, {"name": "3000K", "id": "103"}, {"name": "4000K", "id": "104"}, {"name": "6000K", "id": "105"} ], "Voltage": [ {"name": "24V", "id": "106"} ], "IP Rating": [ {"name": "IP65", "id": "107"} ], "Dimension": [ {"name": "10mm (W) x 10mm (H)", "id": "108"} ], "Length": [ {"name": "5,000mm (L)", "id": "109"} ], "Finish": [ {"name": "Black", "id": "110"} ] }, "Constraints": {}, "sku_mappings": [ { "sku": "TV1010-10W-2.7K-IP65-Black", "combination": ["101", "102", "106", "107", "108", "109", "110"] }, { "sku": "TV1010-10W-3K-IP65-Black", "combination": ["101", "103", "106", "107", "108", "109", "110"] }, { "sku": "TV1010-10W-4K-IP65-Black", "combination": ["101", "104", "106", "107", "108", "109", "110"] }, { "sku": "TV1010-10W-6K-IP65-Black", "combination": ["101", "105", "106", "107", "108", "109", "110"] } ] }</v>
       </c>
       <c r="U2" s="15" t="s">
         <v>42</v>
       </c>
       <c r="V2" s="16" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Extract options object from the json"", U2)"),"{""Power Consumption Rate"": [{""name"": ""10W/m"", ""id"": ""101""}], ""CCT"": [{""name"": ""2700K"", ""id"": ""102""}, {""name"": ""3000K"", ""id"": ""103""}, {""name"": ""4000K"", ""id"": ""104""}, {""name"": ""6000K"", ""id"": ""105""}], ""Voltage"": "&amp;"[{""name"": ""24V"", ""id"": ""106""}], ""IP Rating"": [{""name"": ""IP65"", ""id"": ""107""}], ""Dimension"": [{""name"": ""10mm (W) x 10mm (H)"", ""id"": ""108""}], ""Length"": [{""name"": ""5,000mm (L)"", ""id"": ""109""}], ""Finish"": [{""name"": ""Bl"&amp;"ack"", ""id"": ""110""}]}")</f>
-        <v>{"Power Consumption Rate": [{"name": "10W/m", "id": "101"}], "CCT": [{"name": "2700K", "id": "102"}, {"name": "3000K", "id": "103"}, {"name": "4000K", "id": "104"}, {"name": "6000K", "id": "105"}], "Voltage": [{"name": "24V", "id": "106"}], "IP Rating": [{"name": "IP65", "id": "107"}], "Dimension": [{"name": "10mm (W) x 10mm (H)", "id": "108"}], "Length": [{"name": "5,000mm (L)", "id": "109"}], "Finish": [{"name": "Black", "id": "110"}]}</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Extract options object from the json"", U2)"),"{""Power Consumption Rate"": [{""name"": ""10W/m"", ""id"": ""101""}], ""Color Temperature"": [{""name"": ""2700K"", ""id"": ""102""}, {""name"": ""3000K"", ""id"": ""103""}, {""name"": ""4000K"", ""id"": ""104""}, {""name"": ""6000K"", ""id"": ""105""}],"&amp;" ""Voltage"": [{""name"": ""24V"", ""id"": ""106""}], ""IP Rating"": [{""name"": ""IP65"", ""id"": ""107""}], ""Dimension"": [{""name"": ""10mm (W) x 10mm (H)"", ""id"": ""108""}], ""Length"": [{""name"": ""5,000mm (L)"", ""id"": ""109""}], ""Finish"": [{"&amp;"""name"": ""Black"", ""id"": ""110""}]}")</f>
+        <v>{"Power Consumption Rate": [{"name": "10W/m", "id": "101"}], "Color Temperature": [{"name": "2700K", "id": "102"}, {"name": "3000K", "id": "103"}, {"name": "4000K", "id": "104"}, {"name": "6000K", "id": "105"}], "Voltage": [{"name": "24V", "id": "106"}], "IP Rating": [{"name": "IP65", "id": "107"}], "Dimension": [{"name": "10mm (W) x 10mm (H)", "id": "108"}], "Length": [{"name": "5,000mm (L)", "id": "109"}], "Finish": [{"name": "Black", "id": "110"}]}</v>
       </c>
       <c r="W2" s="16" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Extract constraints object from the json"", U2)"),"{}")</f>
@@ -1083,54 +1054,91 @@
 ### SCHEMA DEFINITIONS
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
-- Light Color (Example Warm White, RGBW, TW, RGB, RED)
-- CCT (Example 3000K, 4000K)
-- Voltage (Example 20V, 12V/24V)
+- Color Temperature (Example 2200K, 2700K, 3000K, 4000K, 5300K, RGBW (3000K), TW (2700K-5300K), TW (2700K-6500K), 2700K &amp; 3000K, RGB, RED, RGB+TW (2700K-6500K), 2700K-4000K, 2300K-4000K)
+- Voltage (Example "&amp;"20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68, IP20)
-- Impact Strength ("&amp;"Example IK10, IK10 with Neon-AluProfile-1617)
+- Impact Strength (Example IK10, IK10 with Neon-AluProfile-1617)
 - Optics (Example SYS30°)
-- Finish (Example Black finish, Silver)
-- Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
-- Dimension (Example 53mm (W) x 14mm"&amp;" (H), 480mm (L) x 240mm (W))
+- Finish (Example Black, Silver)
+- Channel Configuration (Example Singel-Sided, "&amp;"Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
+- Dimension (Example 53mm (W) x 14mm (H), 480mm (L) x 240mm (W))
 - Length (Example Max 11,000mm (L), 5,000mm (L))
-- Strip Width (Example 8mm, 12mm, 8mm (W))
-- Depth (Example 13mm (D))
+- Strip Width (Example 8mm, 12mm)
 - Power Consumption Rate (Example 8W/m, 5W/m)
-- Profile Length (Example 1,000mm)
-- AC Phase-Cut (Example Tr"&amp;"iac)
+-"&amp;" Profile Length (Example 1,000mm)
+- AC Phase-Cut (Example Triac)
 - Current Sinking (Example 0-10V)
 - Current Sourcing (Example 1-10V)
 - Duty Cycle (Example PWM)
 - Variable Resistance (Example Potentiometer)
-- Resolution (Example 12 Pixels/m)
-- Control Protocol (Example DMX, SPI)
+- Pixel (Example 12 Pixels/m)
+- Control Protocol"&amp;" (Example DMX, SPI)
 - Cut Interval (Example Free Cut)
--"&amp;" Glare Control (Example Honeycomb Anti Glare Louvre)
+- Glare Control (Example Honeycomb Anti Glare Louvre)
 - Beam Angle (Example 30°, 36°, 360°)
+- View (Example Top View, Side View)
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding labels mentioned above separated by pipes ('|'). 
+1. Output ONLY the corresponding labels mentio"&amp;"ned above separated by pipes ('|'). 
 2. Do not include the values in your output.
-3. Do not i"&amp;"nclude any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the number of values provided in the input.
+3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
+4. The number of labels in your output must exactly match the number of value"&amp;"s provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-In"&amp;"put: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black finish
+Input: 1.2W | SYM30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black"&amp;"
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
-Generate outpu"&amp;"t for the values text ""&amp;M3)"),"Power Consumption Rate | CCT | Voltage | IP Rating | Dimension | Length | Finish")</f>
-        <v>Power Consumption Rate | CCT | Voltage | IP Rating | Dimension | Length | Finish</v>
+Generate output for the values text ""&amp;M3)"),"Power Consumption Rate | Color Temperature | Voltage | IP Rating | Dimension | Length | Finish")</f>
+        <v>Power Consumption Rate | Color Temperature | Voltage | IP Rating | Dimension | Length | Finish</v>
       </c>
       <c r="O3" s="21" t="s">
         <v>39</v>
       </c>
       <c r="P3" s="12" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N3&amp;"" and values ""&amp;M3&amp;"" separated by character '|' and Using ""&amp;L3&amp;"" and key as 'SKU', Create a JSON object"")"),"{ ""SKU"": ""TV1010-10W-3K-IP65-Black"", ""Power Consumption Rate"": ""10W/m"", ""CCT"": ""3000K"", ""Voltage"": ""24V"", ""IP Rating"": ""IP65"", ""Dimension"": ""10mm (W) x 10mm (H)"", ""Length"": ""5,000mm (L)"", ""Finish"": ""Black"" }")</f>
-        <v>{ "SKU": "TV1010-10W-3K-IP65-Black", "Power Consumption Rate": "10W/m", "CCT": "3000K", "Voltage": "24V", "IP Rating": "IP65", "Dimension": "10mm (W) x 10mm (H)", "Length": "5,000mm (L)", "Finish": "Black" }</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O3&amp;"", Values: ""&amp;M3&amp; "" and SKU Code: ""&amp;L3"&amp;")"),"{
+""Power Consumption Rate"": ""10W/m"",
+""Color Temperature"": ""3000K"",
+""Voltage"": ""24V"",
+""IP Rating"": ""IP65"",
+""Dimension"": ""10mm (W) x 10mm (H)"",
+""Length"": ""5,000mm (L)"",
+""Finish"": ""Black"",
+""SKU"": ""TV1010-10W-3K-IP65-Black""
+}")</f>
+        <v>{
+"Power Consumption Rate": "10W/m",
+"Color Temperature": "3000K",
+"Voltage": "24V",
+"IP Rating": "IP65",
+"Dimension": "10mm (W) x 10mm (H)",
+"Length": "5,000mm (L)",
+"Finish": "Black",
+"SKU": "TV1010-10W-3K-IP65-Black"
+}</v>
       </c>
       <c r="Q3" s="21" t="s">
         <v>49</v>
@@ -1178,54 +1186,91 @@
 ### SCHEMA DEFINITIONS
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
-- Light Color (Example Warm White, RGBW, TW, RGB, RED)
-- CCT (Example 3000K, 4000K)
-- Voltage (Example 20V, 12V/24V)
+- Color Temperature (Example 2200K, 2700K, 3000K, 4000K, 5300K, RGBW (3000K), TW (2700K-5300K), TW (2700K-6500K), 2700K &amp; 3000K, RGB, RED, RGB+TW (2700K-6500K), 2700K-4000K, 2300K-4000K)
+- Voltage (Example "&amp;"20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68, IP20)
-- Impact Strength ("&amp;"Example IK10, IK10 with Neon-AluProfile-1617)
+- Impact Strength (Example IK10, IK10 with Neon-AluProfile-1617)
 - Optics (Example SYS30°)
-- Finish (Example Black finish, Silver)
-- Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
-- Dimension (Example 53mm (W) x 14mm"&amp;" (H), 480mm (L) x 240mm (W))
+- Finish (Example Black, Silver)
+- Channel Configuration (Example Singel-Sided, "&amp;"Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
+- Dimension (Example 53mm (W) x 14mm (H), 480mm (L) x 240mm (W))
 - Length (Example Max 11,000mm (L), 5,000mm (L))
-- Strip Width (Example 8mm, 12mm, 8mm (W))
-- Depth (Example 13mm (D))
+- Strip Width (Example 8mm, 12mm)
 - Power Consumption Rate (Example 8W/m, 5W/m)
-- Profile Length (Example 1,000mm)
-- AC Phase-Cut (Example Tr"&amp;"iac)
+-"&amp;" Profile Length (Example 1,000mm)
+- AC Phase-Cut (Example Triac)
 - Current Sinking (Example 0-10V)
 - Current Sourcing (Example 1-10V)
 - Duty Cycle (Example PWM)
 - Variable Resistance (Example Potentiometer)
-- Resolution (Example 12 Pixels/m)
-- Control Protocol (Example DMX, SPI)
+- Pixel (Example 12 Pixels/m)
+- Control Protocol"&amp;" (Example DMX, SPI)
 - Cut Interval (Example Free Cut)
--"&amp;" Glare Control (Example Honeycomb Anti Glare Louvre)
+- Glare Control (Example Honeycomb Anti Glare Louvre)
 - Beam Angle (Example 30°, 36°, 360°)
+- View (Example Top View, Side View)
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding labels mentioned above separated by pipes ('|'). 
+1. Output ONLY the corresponding labels mentio"&amp;"ned above separated by pipes ('|'). 
 2. Do not include the values in your output.
-3. Do not i"&amp;"nclude any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the number of values provided in the input.
+3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
+4. The number of labels in your output must exactly match the number of value"&amp;"s provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-In"&amp;"put: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black finish
+Input: 1.2W | SYM30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black"&amp;"
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
-Generate outpu"&amp;"t for the values text ""&amp;M4)"),"Power Consumption Rate | CCT | Voltage | IP Rating | Dimension | Length | Finish")</f>
-        <v>Power Consumption Rate | CCT | Voltage | IP Rating | Dimension | Length | Finish</v>
+Generate output for the values text ""&amp;M4)"),"Power Consumption Rate | Color Temperature | Voltage | IP Rating | Dimension | Length | Finish")</f>
+        <v>Power Consumption Rate | Color Temperature | Voltage | IP Rating | Dimension | Length | Finish</v>
       </c>
       <c r="O4" s="21" t="s">
         <v>39</v>
       </c>
       <c r="P4" s="12" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N4&amp;"" and values ""&amp;M4&amp;"" separated by character '|' and Using ""&amp;L4&amp;"" and key as 'SKU', Create a JSON object"")"),"{ ""SKU"": ""TV1010-10W-4K-IP65-Black"", ""Power Consumption Rate"": ""10W/m"", ""CCT"": ""4000K"", ""Voltage"": ""24V"", ""IP Rating"": ""IP65"", ""Dimension"": ""10mm (W) x 10mm (H)"", ""Length"": ""5,000mm (L)"", ""Finish"": ""Black"" }")</f>
-        <v>{ "SKU": "TV1010-10W-4K-IP65-Black", "Power Consumption Rate": "10W/m", "CCT": "4000K", "Voltage": "24V", "IP Rating": "IP65", "Dimension": "10mm (W) x 10mm (H)", "Length": "5,000mm (L)", "Finish": "Black" }</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O4&amp;"", Values: ""&amp;M4&amp; "" and SKU Code: ""&amp;L4"&amp;")"),"{
+""Power Consumption Rate"": ""10W/m"",
+""Color Temperature"": ""4000K"",
+""Voltage"": ""24V"",
+""IP Rating"": ""IP65"",
+""Dimension"": ""10mm (W) x 10mm (H)"",
+""Length"": ""5,000mm (L)"",
+""Finish"": ""Black"",
+""SKU"": ""TV1010-10W-4K-IP65-Black""
+}")</f>
+        <v>{
+"Power Consumption Rate": "10W/m",
+"Color Temperature": "4000K",
+"Voltage": "24V",
+"IP Rating": "IP65",
+"Dimension": "10mm (W) x 10mm (H)",
+"Length": "5,000mm (L)",
+"Finish": "Black",
+"SKU": "TV1010-10W-4K-IP65-Black"
+}</v>
       </c>
       <c r="Q4" s="21" t="s">
         <v>53</v>
@@ -1273,54 +1318,91 @@
 ### SCHEMA DEFINITIONS
 1. Global Core Fields (Every "&amp;"SKU must have these):
 - Power (Example 1.2W, 7W)
-- Light Color (Example Warm White, RGBW, TW, RGB, RED)
-- CCT (Example 3000K, 4000K)
-- Voltage (Example 20V, 12V/24V)
+- Color Temperature (Example 2200K, 2700K, 3000K, 4000K, 5300K, RGBW (3000K), TW (2700K-5300K), TW (2700K-6500K), 2700K &amp; 3000K, RGB, RED, RGB+TW (2700K-6500K), 2700K-4000K, 2300K-4000K)
+- Voltage (Example "&amp;"20V, 12V/24V)
 - Current Type (Example AC/DC)
 - IP Rating (Example IP67, IP68, IP20)
-- Impact Strength ("&amp;"Example IK10, IK10 with Neon-AluProfile-1617)
+- Impact Strength (Example IK10, IK10 with Neon-AluProfile-1617)
 - Optics (Example SYS30°)
-- Finish (Example Black finish, Silver)
-- Channel Configuration (Example Singel-Sided, Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
-- Dimension (Example 53mm (W) x 14mm"&amp;" (H), 480mm (L) x 240mm (W))
+- Finish (Example Black, Silver)
+- Channel Configuration (Example Singel-Sided, "&amp;"Double-Sided, Bendable Single-Sided, Bendable Double-Sided)
+- Dimension (Example 53mm (W) x 14mm (H), 480mm (L) x 240mm (W))
 - Length (Example Max 11,000mm (L), 5,000mm (L))
-- Strip Width (Example 8mm, 12mm, 8mm (W))
-- Depth (Example 13mm (D))
+- Strip Width (Example 8mm, 12mm)
 - Power Consumption Rate (Example 8W/m, 5W/m)
-- Profile Length (Example 1,000mm)
-- AC Phase-Cut (Example Tr"&amp;"iac)
+-"&amp;" Profile Length (Example 1,000mm)
+- AC Phase-Cut (Example Triac)
 - Current Sinking (Example 0-10V)
 - Current Sourcing (Example 1-10V)
 - Duty Cycle (Example PWM)
 - Variable Resistance (Example Potentiometer)
-- Resolution (Example 12 Pixels/m)
-- Control Protocol (Example DMX, SPI)
+- Pixel (Example 12 Pixels/m)
+- Control Protocol"&amp;" (Example DMX, SPI)
 - Cut Interval (Example Free Cut)
--"&amp;" Glare Control (Example Honeycomb Anti Glare Louvre)
+- Glare Control (Example Honeycomb Anti Glare Louvre)
 - Beam Angle (Example 30°, 36°, 360°)
+- View (Example Top View, Side View)
 ### STRICT OUTPUT RULES
-1. Output ONLY the corresponding labels mentioned above separated by pipes ('|'). 
+1. Output ONLY the corresponding labels mentio"&amp;"ned above separated by pipes ('|'). 
 2. Do not include the values in your output.
-3. Do not i"&amp;"nclude any conversational text, introductory remarks, or markdown formatting blocks.
-4. The number of labels in your output must exactly match the number of values provided in the input.
+3. Do not include any conversational text, introductory remarks, or markdown formatting blocks.
+4. The number of labels in your output must exactly match the number of value"&amp;"s provided in the input.
 ---
 ### FEW-SHOT EXAMPLES
 #### Example 1 (Standard Neon Strip)
-In"&amp;"put: 1.2W | SYM30° | 3000K | IP67 | IK10
-Output: Power|Optics|CCT|IP Rating|Impact Strength
-Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black finish
+Input: 1.2W | SYM30° | 3000K | IP67 | IK10
+Output: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Input: 7W | Warm White | 12V/24V | AC/DC | IP67 | Black"&amp;"
 Output: Power | Light Color | Current Type | IP Rating | Finish
 ---
 ### YOUR TASK
-Generate outpu"&amp;"t for the values text ""&amp;M5)"),"Power Consumption Rate | CCT | Voltage | IP Rating | Dimension | Length | Finish")</f>
-        <v>Power Consumption Rate | CCT | Voltage | IP Rating | Dimension | Length | Finish</v>
+Generate output for the values text ""&amp;M5)"),"Power Consumption Rate | Color Temperature | Voltage | IP Rating | Dimension | Length | Finish")</f>
+        <v>Power Consumption Rate | Color Temperature | Voltage | IP Rating | Dimension | Length | Finish</v>
       </c>
       <c r="O5" s="21" t="s">
         <v>39</v>
       </c>
       <c r="P5" s="12" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Using the labels""&amp;N5&amp;"" and values ""&amp;M5&amp;"" separated by character '|' and Using ""&amp;L5&amp;"" and key as 'SKU', Create a JSON object"")"),"{ ""SKU"": ""TV1010-10W-6K-IP65-Black"", ""Power Consumption Rate"": ""10W/m"", ""CCT"": ""6000K"", ""Voltage"": ""24V"", ""IP Rating"": ""IP65"", ""Dimension"": ""10mm (W) x 10mm (H)"", ""Length"": ""5,000mm (L)"", ""Finish"": ""Black"" }")</f>
-        <v>{ "SKU": "TV1010-10W-6K-IP65-Black", "Power Consumption Rate": "10W/m", "CCT": "6000K", "Voltage": "24V", "IP Rating": "IP65", "Dimension": "10mm (W) x 10mm (H)", "Length": "5,000mm (L)", "Finish": "Black" }</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""You are a data processing assistant that converts delimited text into structured JSON.
+Task: Convert the provided pipe-delimited (|) header and value lines into a valid JSON object or array of objects.
+Instructions:
+- Clean both keys and values by "&amp;"trimming leading and trailing whitespace.
+- Remove any index prefix from the value string (e.g., convert 1.2W from 1.2W  or 1.2W without leading list numbers).
+- Map each key from Line 1 to its corresponding value in Line 2.
+- Output only valid, properly "&amp;"formatted JSON with no surrounding commentary or explanation.
+Example:
+Keys: Power|Optics|Color Temperature|IP Rating|Impact Strength
+Values: 1.2W | SYM 30° | 4000K | IP67 | IK10
+SKU Code: HRS001
+Example Output:
+{
+  """"Power"""": """"1.2W"""",
+  """"Op"&amp;"tics"""": """"SYM 30°"""",
+  """"Color Temperature"""": """"4000K"""",
+  """"IP Rating"""": """"IP67"""",
+  """"Impact Strength"""": """"IK10"""",
+  """"SKU"""": """"HRS001""""
+}
+Generate JSON for the Keys: ""&amp;O5&amp;"", Values: ""&amp;M5&amp; "" and SKU Code: ""&amp;L5"&amp;")"),"{
+""Power Consumption Rate"": ""10W/m"",
+""Color Temperature"": ""6000K"",
+""Voltage"": ""24V"",
+""IP Rating"": ""IP65"",
+""Dimension"": ""10mm (W) x 10mm (H)"",
+""Length"": ""5,000mm (L)"",
+""Finish"": ""Black"",
+""SKU"": ""TV1010-10W-6K-IP65-Black""
+}")</f>
+        <v>{
+"Power Consumption Rate": "10W/m",
+"Color Temperature": "6000K",
+"Voltage": "24V",
+"IP Rating": "IP65",
+"Dimension": "10mm (W) x 10mm (H)",
+"Length": "5,000mm (L)",
+"Finish": "Black",
+"SKU": "TV1010-10W-6K-IP65-Black"
+}</v>
       </c>
       <c r="Q5" s="21" t="s">
         <v>57</v>
